--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.671</v>
+        <v>0.67</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>580.29</v>
+        <v>576.91</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>525.74</v>
+        <v>524.1900000000001</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.104</v>
+        <v>0.101</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.604</v>
+        <v>0.601</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04974999904632568</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230790753.7566097</v>
+        <v>230790748.8200843</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>525.74</v>
+        <v>524.1900000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>121335930880</v>
+        <v>120978202624</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.37</v>
+        <v>19.34</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>14.37</v>
+        <v>14.23</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>106100932608</v>
+        <v>106569711616</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.435497</v>
+        <v>24.49863</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>16.765</v>
+        <v>16.823</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.897</v>
+        <v>4.914</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>166602096640</v>
+        <v>166333366272</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>75.55197</v>
+        <v>75.70144000000001</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-65.84699999999999</v>
+        <v>-67.387</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.032</v>
+        <v>2.079</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>184032821248</v>
+        <v>182196666368</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>37.98275</v>
+        <v>37.603786</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>25.865</v>
+        <v>25.796</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.641</v>
+        <v>4.629</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>96560504832</v>
+        <v>96291299328</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>21.76189</v>
+        <v>21.687994</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.204</v>
+        <v>15.271</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.838</v>
+        <v>1.846</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>64373682176</v>
+        <v>64135979008</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>7.811923</v>
+        <v>7.783077</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>10.592</v>
+        <v>10.599</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>2.369</v>
+        <v>2.371</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>45922390016</v>
+        <v>45723136000</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>24.884966</v>
+        <v>24.802021</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>28.883</v>
+        <v>28.591</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>4.821</v>
+        <v>4.773</v>
       </c>
     </row>
     <row r="12">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>73999212544</v>
+        <v>73726443520</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>16.56248</v>
+        <v>16.501429</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.194</v>
+        <v>12.195</v>
       </c>
       <c r="F12" s="34" t="n">
         <v>2.063</v>
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>119645003776</v>
+        <v>119774085120</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>33.30547</v>
+        <v>33.32971</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>22.248</v>
+        <v>22.602</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.861</v>
+        <v>5.954</v>
       </c>
     </row>
     <row r="15">
